--- a/QUẢN LÝ NHÂN SỰ/Nhân viên/Bắc đảo/VIN TRƯƠNG VŨ CA/Kết toán cho a linh.xlsx
+++ b/QUẢN LÝ NHÂN SỰ/Nhân viên/Bắc đảo/VIN TRƯƠNG VŨ CA/Kết toán cho a linh.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A28721-2D03-4A7A-B5E5-3A723E1D216F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA49795-8C82-4F4C-8EFC-0F019F4B6A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>CÔNG TY TNHH MTV VẬN TẢI VÀ DU LỊCH MINH HẢI</t>
   </si>
@@ -113,9 +113,6 @@
     <t>1,93 tháng</t>
   </si>
   <si>
-    <t>-1,550,000</t>
-  </si>
-  <si>
     <t>DOANH THU NGÀY 08-02-2026 PHẢI NỘP CHO CTY</t>
   </si>
   <si>
@@ -129,6 +126,12 @@
   </si>
   <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>TIỀN DOANH THU ANH TÌNH CÒN THIẾU</t>
+  </si>
+  <si>
+    <t>-2,090,000</t>
   </si>
 </sst>
 </file>
@@ -438,9 +441,6 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -473,6 +473,9 @@
           <color indexed="64"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -687,8 +690,8 @@
   </autoFilter>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="NỘI DUNG" dataDxfId="4" dataCellStyle="Description"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="SỐ LƯỢNG " totalsRowLabel=" TỔNG CHI PHÍ TRỪ " dataDxfId="3" totalsRowDxfId="2" dataCellStyle="Description"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="TỔNG SỐ" totalsRowLabel="-1,550,000" dataDxfId="1" totalsRowDxfId="0" dataCellStyle="Currency"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="SỐ LƯỢNG " totalsRowLabel=" TỔNG CHI PHÍ TRỪ " dataDxfId="3" totalsRowDxfId="1" dataCellStyle="Description"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="TỔNG SỐ" totalsRowLabel="-2,090,000" dataDxfId="2" totalsRowDxfId="0" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="Invoice that calculates total" showFirstColumn="0" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -1107,7 +1110,7 @@
       </c>
       <c r="D3" s="7">
         <f ca="1">TODAY()</f>
-        <v>46062</v>
+        <v>46063</v>
       </c>
     </row>
     <row r="4" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1138,18 +1141,18 @@
         <v>14</v>
       </c>
       <c r="K6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -1197,7 +1200,7 @@
     </row>
     <row r="15" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" s="8">
         <v>1</v>
@@ -1206,13 +1209,19 @@
         <v>-600000</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="9"/>
+      <c r="B16" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="8">
+        <v>1</v>
+      </c>
+      <c r="D16" s="9">
+        <v>-540000</v>
+      </c>
       <c r="F16" s="12"/>
     </row>
     <row r="17" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -1220,7 +1229,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -1229,7 +1238,7 @@
       </c>
       <c r="D18" s="10">
         <f>SUBTOTAL(109,Invoice[TỔNG SỐ])</f>
-        <v>1450000</v>
+        <v>910000</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -1295,26 +1304,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="26" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac37c1753acd5e330d2062ccec26ea66">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3b340c7101c92c5120abd06486f94548" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -1614,6 +1603,26 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1624,18 +1633,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B8768FD-A897-4E96-A3F0-B7D93590B1CF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{565030E0-6AB1-4C95-ADA8-2C257F6CE35D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1656,6 +1653,18 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B8768FD-A897-4E96-A3F0-B7D93590B1CF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69C393F6-8D9A-4F59-A33D-C9C2FA7EFF8E}">
   <ds:schemaRefs>
